--- a/test/enum_standard_mapping/output_dpr_first100.xlsx
+++ b/test/enum_standard_mapping/output_dpr_first100.xlsx
@@ -528,7 +528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF102"/>
+  <dimension ref="A1:AE102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="5" customWidth="1" style="17" min="1" max="1"/>
@@ -729,11 +729,6 @@
           <t>LLM判断过程</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>候选及得分</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="J3" t="inlineStr">
@@ -776,7 +771,6 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr"/>
-      <c r="AF3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="J4" t="inlineStr">
@@ -819,7 +813,6 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr"/>
-      <c r="AF4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="J5" t="inlineStr">
@@ -867,7 +860,6 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr"/>
-      <c r="AF5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="J6" t="inlineStr">
@@ -915,7 +907,6 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr"/>
-      <c r="AF6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="J7" t="inlineStr">
@@ -963,7 +954,6 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="inlineStr"/>
-      <c r="AF7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="J8" t="inlineStr">
@@ -1011,7 +1001,6 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="inlineStr"/>
-      <c r="AF8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="J9" t="inlineStr">
@@ -1054,7 +1043,6 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="inlineStr"/>
-      <c r="AF9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="J10" t="inlineStr">
@@ -1097,7 +1085,6 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="inlineStr"/>
-      <c r="AF10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="J11" t="inlineStr">
@@ -1153,7 +1140,6 @@
           <t>枚举值召回无候选枚举代码，判定新增枚举代码并新增标准</t>
         </is>
       </c>
-      <c r="AF11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="J12" t="inlineStr">
@@ -1209,7 +1195,6 @@
           <t>枚举值召回无候选枚举代码，判定新增枚举代码并新增标准</t>
         </is>
       </c>
-      <c r="AF12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="J13" t="inlineStr">
@@ -1257,7 +1242,6 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr"/>
       <c r="AE13" t="inlineStr"/>
-      <c r="AF13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="J14" t="inlineStr">
@@ -1300,7 +1284,6 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr"/>
       <c r="AE14" t="inlineStr"/>
-      <c r="AF14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="J15" t="inlineStr">
@@ -1343,7 +1326,6 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="inlineStr"/>
-      <c r="AF15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="J16" t="inlineStr">
@@ -1386,7 +1368,6 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="inlineStr"/>
-      <c r="AF16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="J17" t="inlineStr">
@@ -1429,7 +1410,6 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr"/>
       <c r="AE17" t="inlineStr"/>
-      <c r="AF17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="J18" t="inlineStr">
@@ -1472,7 +1452,6 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr"/>
       <c r="AE18" t="inlineStr"/>
-      <c r="AF18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="J19" t="inlineStr">
@@ -1515,7 +1494,6 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr"/>
       <c r="AE19" t="inlineStr"/>
-      <c r="AF19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="J20" t="inlineStr">
@@ -1558,7 +1536,6 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr"/>
       <c r="AE20" t="inlineStr"/>
-      <c r="AF20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="J21" t="inlineStr">
@@ -1599,7 +1576,6 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr"/>
       <c r="AE21" t="inlineStr"/>
-      <c r="AF21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="J22" t="inlineStr">
@@ -1640,7 +1616,6 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr"/>
       <c r="AE22" t="inlineStr"/>
-      <c r="AF22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="J23" t="inlineStr">
@@ -1683,7 +1658,6 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr"/>
       <c r="AE23" t="inlineStr"/>
-      <c r="AF23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="J24" t="inlineStr">
@@ -1726,7 +1700,6 @@
       <c r="AC24" t="inlineStr"/>
       <c r="AD24" t="inlineStr"/>
       <c r="AE24" t="inlineStr"/>
-      <c r="AF24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="J25" t="inlineStr">
@@ -1769,7 +1742,6 @@
       <c r="AC25" t="inlineStr"/>
       <c r="AD25" t="inlineStr"/>
       <c r="AE25" t="inlineStr"/>
-      <c r="AF25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="J26" t="inlineStr">
@@ -1812,7 +1784,6 @@
       <c r="AC26" t="inlineStr"/>
       <c r="AD26" t="inlineStr"/>
       <c r="AE26" t="inlineStr"/>
-      <c r="AF26" t="inlineStr"/>
     </row>
     <row r="27" customFormat="1" s="13">
       <c r="J27" s="13" t="inlineStr">
@@ -1853,7 +1824,6 @@
       <c r="AC27" t="inlineStr"/>
       <c r="AD27" t="inlineStr"/>
       <c r="AE27" t="inlineStr"/>
-      <c r="AF27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="J28" t="inlineStr">
@@ -1894,7 +1864,6 @@
       <c r="AC28" t="inlineStr"/>
       <c r="AD28" t="inlineStr"/>
       <c r="AE28" t="inlineStr"/>
-      <c r="AF28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="J29" t="inlineStr">
@@ -1942,7 +1911,6 @@
       <c r="AC29" t="inlineStr"/>
       <c r="AD29" t="inlineStr"/>
       <c r="AE29" t="inlineStr"/>
-      <c r="AF29" t="inlineStr"/>
     </row>
     <row r="30" customFormat="1" s="9">
       <c r="J30" s="9" t="inlineStr">
@@ -1990,7 +1958,6 @@
       <c r="AC30" t="inlineStr"/>
       <c r="AD30" t="inlineStr"/>
       <c r="AE30" t="inlineStr"/>
-      <c r="AF30" t="inlineStr"/>
     </row>
     <row r="31" customFormat="1" s="13">
       <c r="J31" s="13" t="inlineStr">
@@ -2033,7 +2000,6 @@
       <c r="AC31" t="inlineStr"/>
       <c r="AD31" t="inlineStr"/>
       <c r="AE31" t="inlineStr"/>
-      <c r="AF31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="J32" t="inlineStr">
@@ -2076,7 +2042,6 @@
       <c r="AC32" t="inlineStr"/>
       <c r="AD32" t="inlineStr"/>
       <c r="AE32" t="inlineStr"/>
-      <c r="AF32" t="inlineStr"/>
     </row>
     <row r="33" ht="30" customFormat="1" customHeight="1" s="9">
       <c r="J33" s="12" t="inlineStr">
@@ -2132,7 +2097,6 @@
           <t>枚举值召回无候选枚举代码，判定新增枚举代码并新增标准</t>
         </is>
       </c>
-      <c r="AF33" t="inlineStr"/>
     </row>
     <row r="34" ht="30" customHeight="1" s="17">
       <c r="J34" s="1" t="inlineStr">
@@ -2176,7 +2140,6 @@
       <c r="AC34" t="inlineStr"/>
       <c r="AD34" t="inlineStr"/>
       <c r="AE34" t="inlineStr"/>
-      <c r="AF34" t="inlineStr"/>
     </row>
     <row r="35" ht="30" customHeight="1" s="17">
       <c r="J35" s="1" t="inlineStr">
@@ -2220,7 +2183,6 @@
       <c r="AC35" t="inlineStr"/>
       <c r="AD35" t="inlineStr"/>
       <c r="AE35" t="inlineStr"/>
-      <c r="AF35" t="inlineStr"/>
     </row>
     <row r="36" ht="30" customHeight="1" s="17">
       <c r="J36" s="1" t="inlineStr">
@@ -2264,7 +2226,6 @@
       <c r="AC36" t="inlineStr"/>
       <c r="AD36" t="inlineStr"/>
       <c r="AE36" t="inlineStr"/>
-      <c r="AF36" t="inlineStr"/>
     </row>
     <row r="37" ht="30" customHeight="1" s="17">
       <c r="J37" s="1" t="inlineStr">
@@ -2308,7 +2269,6 @@
       <c r="AC37" t="inlineStr"/>
       <c r="AD37" t="inlineStr"/>
       <c r="AE37" t="inlineStr"/>
-      <c r="AF37" t="inlineStr"/>
     </row>
     <row r="38" ht="30" customHeight="1" s="17">
       <c r="J38" s="1" t="inlineStr">
@@ -2352,7 +2312,6 @@
       <c r="AC38" t="inlineStr"/>
       <c r="AD38" t="inlineStr"/>
       <c r="AE38" t="inlineStr"/>
-      <c r="AF38" t="inlineStr"/>
     </row>
     <row r="39" ht="30" customHeight="1" s="17">
       <c r="J39" s="1" t="inlineStr">
@@ -2396,7 +2355,6 @@
       <c r="AC39" t="inlineStr"/>
       <c r="AD39" t="inlineStr"/>
       <c r="AE39" t="inlineStr"/>
-      <c r="AF39" t="inlineStr"/>
     </row>
     <row r="40" ht="30" customHeight="1" s="17">
       <c r="J40" s="1" t="inlineStr">
@@ -2440,7 +2398,6 @@
       <c r="AC40" t="inlineStr"/>
       <c r="AD40" t="inlineStr"/>
       <c r="AE40" t="inlineStr"/>
-      <c r="AF40" t="inlineStr"/>
     </row>
     <row r="41" ht="30" customHeight="1" s="17">
       <c r="J41" s="1" t="inlineStr">
@@ -2484,7 +2441,6 @@
       <c r="AC41" t="inlineStr"/>
       <c r="AD41" t="inlineStr"/>
       <c r="AE41" t="inlineStr"/>
-      <c r="AF41" t="inlineStr"/>
     </row>
     <row r="42" ht="30" customHeight="1" s="17">
       <c r="J42" s="1" t="inlineStr">
@@ -2532,7 +2488,6 @@
       <c r="AC42" t="inlineStr"/>
       <c r="AD42" t="inlineStr"/>
       <c r="AE42" t="inlineStr"/>
-      <c r="AF42" t="inlineStr"/>
     </row>
     <row r="43" ht="30" customFormat="1" customHeight="1" s="9">
       <c r="J43" s="12" t="inlineStr">
@@ -2576,7 +2531,6 @@
       <c r="AC43" t="inlineStr"/>
       <c r="AD43" t="inlineStr"/>
       <c r="AE43" t="inlineStr"/>
-      <c r="AF43" t="inlineStr"/>
     </row>
     <row r="44" ht="30" customHeight="1" s="17">
       <c r="J44" s="1" t="inlineStr">
@@ -2620,7 +2574,6 @@
       <c r="AC44" t="inlineStr"/>
       <c r="AD44" t="inlineStr"/>
       <c r="AE44" t="inlineStr"/>
-      <c r="AF44" t="inlineStr"/>
     </row>
     <row r="45" ht="30" customHeight="1" s="17">
       <c r="J45" s="1" t="inlineStr">
@@ -2664,7 +2617,6 @@
       <c r="AC45" t="inlineStr"/>
       <c r="AD45" t="inlineStr"/>
       <c r="AE45" t="inlineStr"/>
-      <c r="AF45" t="inlineStr"/>
     </row>
     <row r="46" ht="30" customHeight="1" s="17">
       <c r="J46" s="1" t="inlineStr">
@@ -2708,7 +2660,6 @@
       <c r="AC46" t="inlineStr"/>
       <c r="AD46" t="inlineStr"/>
       <c r="AE46" t="inlineStr"/>
-      <c r="AF46" t="inlineStr"/>
     </row>
     <row r="47" ht="30" customFormat="1" customHeight="1" s="13">
       <c r="J47" s="19" t="inlineStr">
@@ -2752,7 +2703,6 @@
       <c r="AC47" t="inlineStr"/>
       <c r="AD47" t="inlineStr"/>
       <c r="AE47" t="inlineStr"/>
-      <c r="AF47" t="inlineStr"/>
     </row>
     <row r="48" ht="30" customFormat="1" customHeight="1" s="13">
       <c r="J48" s="19" t="inlineStr">
@@ -2796,7 +2746,6 @@
       <c r="AC48" t="inlineStr"/>
       <c r="AD48" t="inlineStr"/>
       <c r="AE48" t="inlineStr"/>
-      <c r="AF48" t="inlineStr"/>
     </row>
     <row r="49" ht="30" customFormat="1" customHeight="1" s="13">
       <c r="J49" s="19" t="inlineStr">
@@ -2840,7 +2789,6 @@
       <c r="AC49" t="inlineStr"/>
       <c r="AD49" t="inlineStr"/>
       <c r="AE49" t="inlineStr"/>
-      <c r="AF49" t="inlineStr"/>
     </row>
     <row r="50" ht="30" customFormat="1" customHeight="1" s="13">
       <c r="J50" s="19" t="inlineStr">
@@ -2884,7 +2832,6 @@
       <c r="AC50" t="inlineStr"/>
       <c r="AD50" t="inlineStr"/>
       <c r="AE50" t="inlineStr"/>
-      <c r="AF50" t="inlineStr"/>
     </row>
     <row r="51" ht="30" customFormat="1" customHeight="1" s="13">
       <c r="J51" s="19" t="inlineStr">
@@ -2928,7 +2875,6 @@
       <c r="AC51" t="inlineStr"/>
       <c r="AD51" t="inlineStr"/>
       <c r="AE51" t="inlineStr"/>
-      <c r="AF51" t="inlineStr"/>
     </row>
     <row r="52" ht="30" customFormat="1" customHeight="1" s="13">
       <c r="J52" s="19" t="inlineStr">
@@ -2972,7 +2918,6 @@
       <c r="AC52" t="inlineStr"/>
       <c r="AD52" t="inlineStr"/>
       <c r="AE52" t="inlineStr"/>
-      <c r="AF52" t="inlineStr"/>
     </row>
     <row r="53" ht="30" customFormat="1" customHeight="1" s="13">
       <c r="J53" s="19" t="inlineStr">
@@ -3016,7 +2961,6 @@
       <c r="AC53" t="inlineStr"/>
       <c r="AD53" t="inlineStr"/>
       <c r="AE53" t="inlineStr"/>
-      <c r="AF53" t="inlineStr"/>
     </row>
     <row r="54" ht="30" customFormat="1" customHeight="1" s="13">
       <c r="J54" s="19" t="inlineStr">
@@ -3060,7 +3004,6 @@
       <c r="AC54" t="inlineStr"/>
       <c r="AD54" t="inlineStr"/>
       <c r="AE54" t="inlineStr"/>
-      <c r="AF54" t="inlineStr"/>
     </row>
     <row r="55" ht="30" customFormat="1" customHeight="1" s="13">
       <c r="J55" s="19" t="inlineStr">
@@ -3104,7 +3047,6 @@
       <c r="AC55" t="inlineStr"/>
       <c r="AD55" t="inlineStr"/>
       <c r="AE55" t="inlineStr"/>
-      <c r="AF55" t="inlineStr"/>
     </row>
     <row r="56" ht="30" customFormat="1" customHeight="1" s="13">
       <c r="J56" s="19" t="inlineStr">
@@ -3148,7 +3090,6 @@
       <c r="AC56" t="inlineStr"/>
       <c r="AD56" t="inlineStr"/>
       <c r="AE56" t="inlineStr"/>
-      <c r="AF56" t="inlineStr"/>
     </row>
     <row r="57" ht="30" customHeight="1" s="17">
       <c r="J57" s="1" t="inlineStr">
@@ -3192,7 +3133,6 @@
       <c r="AC57" t="inlineStr"/>
       <c r="AD57" t="inlineStr"/>
       <c r="AE57" t="inlineStr"/>
-      <c r="AF57" t="inlineStr"/>
     </row>
     <row r="58" ht="30" customHeight="1" s="17">
       <c r="J58" s="1" t="inlineStr">
@@ -3236,7 +3176,6 @@
       <c r="AC58" t="inlineStr"/>
       <c r="AD58" t="inlineStr"/>
       <c r="AE58" t="inlineStr"/>
-      <c r="AF58" t="inlineStr"/>
     </row>
     <row r="59" ht="30" customHeight="1" s="17">
       <c r="J59" s="1" t="inlineStr">
@@ -3280,7 +3219,6 @@
       <c r="AC59" t="inlineStr"/>
       <c r="AD59" t="inlineStr"/>
       <c r="AE59" t="inlineStr"/>
-      <c r="AF59" t="inlineStr"/>
     </row>
     <row r="60" ht="30" customHeight="1" s="17">
       <c r="J60" s="1" t="inlineStr">
@@ -3324,7 +3262,6 @@
       <c r="AC60" t="inlineStr"/>
       <c r="AD60" t="inlineStr"/>
       <c r="AE60" t="inlineStr"/>
-      <c r="AF60" t="inlineStr"/>
     </row>
     <row r="61" ht="30" customHeight="1" s="17">
       <c r="J61" s="1" t="inlineStr">
@@ -3368,7 +3305,6 @@
       <c r="AC61" t="inlineStr"/>
       <c r="AD61" t="inlineStr"/>
       <c r="AE61" t="inlineStr"/>
-      <c r="AF61" t="inlineStr"/>
     </row>
     <row r="62" ht="30" customHeight="1" s="17">
       <c r="J62" s="1" t="inlineStr">
@@ -3412,7 +3348,6 @@
       <c r="AC62" t="inlineStr"/>
       <c r="AD62" t="inlineStr"/>
       <c r="AE62" t="inlineStr"/>
-      <c r="AF62" t="inlineStr"/>
     </row>
     <row r="63" ht="30" customHeight="1" s="17">
       <c r="J63" s="1" t="inlineStr">
@@ -3456,7 +3391,6 @@
       <c r="AC63" t="inlineStr"/>
       <c r="AD63" t="inlineStr"/>
       <c r="AE63" t="inlineStr"/>
-      <c r="AF63" t="inlineStr"/>
     </row>
     <row r="64" ht="30" customHeight="1" s="17">
       <c r="J64" s="1" t="inlineStr">
@@ -3500,7 +3434,6 @@
       <c r="AC64" t="inlineStr"/>
       <c r="AD64" t="inlineStr"/>
       <c r="AE64" t="inlineStr"/>
-      <c r="AF64" t="inlineStr"/>
     </row>
     <row r="65" ht="30" customHeight="1" s="17">
       <c r="J65" s="1" t="inlineStr">
@@ -3544,7 +3477,6 @@
       <c r="AC65" t="inlineStr"/>
       <c r="AD65" t="inlineStr"/>
       <c r="AE65" t="inlineStr"/>
-      <c r="AF65" t="inlineStr"/>
     </row>
     <row r="66" ht="30" customFormat="1" customHeight="1" s="9">
       <c r="J66" s="12" t="inlineStr">
@@ -3592,7 +3524,6 @@
       <c r="AC66" t="inlineStr"/>
       <c r="AD66" t="inlineStr"/>
       <c r="AE66" t="inlineStr"/>
-      <c r="AF66" t="inlineStr"/>
     </row>
     <row r="67" ht="30" customHeight="1" s="17">
       <c r="J67" s="1" t="inlineStr">
@@ -3636,7 +3567,6 @@
       <c r="AC67" t="inlineStr"/>
       <c r="AD67" t="inlineStr"/>
       <c r="AE67" t="inlineStr"/>
-      <c r="AF67" t="inlineStr"/>
     </row>
     <row r="68" ht="30" customHeight="1" s="17">
       <c r="J68" s="1" t="inlineStr">
@@ -3680,7 +3610,6 @@
       <c r="AC68" t="inlineStr"/>
       <c r="AD68" t="inlineStr"/>
       <c r="AE68" t="inlineStr"/>
-      <c r="AF68" t="inlineStr"/>
     </row>
     <row r="69" ht="30" customHeight="1" s="17">
       <c r="J69" s="1" t="inlineStr">
@@ -3724,7 +3653,6 @@
       <c r="AC69" t="inlineStr"/>
       <c r="AD69" t="inlineStr"/>
       <c r="AE69" t="inlineStr"/>
-      <c r="AF69" t="inlineStr"/>
     </row>
     <row r="70" ht="30" customHeight="1" s="17">
       <c r="J70" s="1" t="inlineStr">
@@ -3768,7 +3696,6 @@
       <c r="AC70" t="inlineStr"/>
       <c r="AD70" t="inlineStr"/>
       <c r="AE70" t="inlineStr"/>
-      <c r="AF70" t="inlineStr"/>
     </row>
     <row r="71" ht="30" customHeight="1" s="17">
       <c r="J71" s="1" t="inlineStr">
@@ -3812,7 +3739,6 @@
       <c r="AC71" t="inlineStr"/>
       <c r="AD71" t="inlineStr"/>
       <c r="AE71" t="inlineStr"/>
-      <c r="AF71" t="inlineStr"/>
     </row>
     <row r="72" ht="30" customHeight="1" s="17">
       <c r="J72" s="1" t="inlineStr">
@@ -3856,7 +3782,6 @@
       <c r="AC72" t="inlineStr"/>
       <c r="AD72" t="inlineStr"/>
       <c r="AE72" t="inlineStr"/>
-      <c r="AF72" t="inlineStr"/>
     </row>
     <row r="73" ht="30" customHeight="1" s="17">
       <c r="J73" s="1" t="inlineStr">
@@ -3900,7 +3825,6 @@
       <c r="AC73" t="inlineStr"/>
       <c r="AD73" t="inlineStr"/>
       <c r="AE73" t="inlineStr"/>
-      <c r="AF73" t="inlineStr"/>
     </row>
     <row r="74" ht="30" customHeight="1" s="17">
       <c r="J74" s="1" t="inlineStr">
@@ -3944,7 +3868,6 @@
       <c r="AC74" t="inlineStr"/>
       <c r="AD74" t="inlineStr"/>
       <c r="AE74" t="inlineStr"/>
-      <c r="AF74" t="inlineStr"/>
     </row>
     <row r="75" ht="30" customHeight="1" s="17">
       <c r="J75" s="1" t="inlineStr">
@@ -3988,7 +3911,6 @@
       <c r="AC75" t="inlineStr"/>
       <c r="AD75" t="inlineStr"/>
       <c r="AE75" t="inlineStr"/>
-      <c r="AF75" t="inlineStr"/>
     </row>
     <row r="76" ht="30" customHeight="1" s="17">
       <c r="J76" s="1" t="inlineStr">
@@ -4032,7 +3954,6 @@
       <c r="AC76" t="inlineStr"/>
       <c r="AD76" t="inlineStr"/>
       <c r="AE76" t="inlineStr"/>
-      <c r="AF76" t="inlineStr"/>
     </row>
     <row r="77" ht="30" customHeight="1" s="17">
       <c r="J77" s="1" t="inlineStr">
@@ -4076,7 +3997,6 @@
       <c r="AC77" t="inlineStr"/>
       <c r="AD77" t="inlineStr"/>
       <c r="AE77" t="inlineStr"/>
-      <c r="AF77" t="inlineStr"/>
     </row>
     <row r="78" ht="30" customHeight="1" s="17">
       <c r="J78" s="1" t="inlineStr">
@@ -4132,7 +4052,6 @@
           <t>枚举值召回无候选枚举代码，判定新增枚举代码并新增标准</t>
         </is>
       </c>
-      <c r="AF78" t="inlineStr"/>
     </row>
     <row r="79" ht="30" customHeight="1" s="17">
       <c r="J79" s="1" t="inlineStr">
@@ -4188,7 +4107,6 @@
           <t>枚举值召回无候选枚举代码，判定新增枚举代码并新增标准</t>
         </is>
       </c>
-      <c r="AF79" t="inlineStr"/>
     </row>
     <row r="80" ht="30" customHeight="1" s="17">
       <c r="J80" s="1" t="inlineStr">
@@ -4232,7 +4150,6 @@
       <c r="AC80" t="inlineStr"/>
       <c r="AD80" t="inlineStr"/>
       <c r="AE80" t="inlineStr"/>
-      <c r="AF80" t="inlineStr"/>
     </row>
     <row r="81" ht="30" customHeight="1" s="17">
       <c r="J81" s="1" t="inlineStr">
@@ -4276,7 +4193,6 @@
       <c r="AC81" t="inlineStr"/>
       <c r="AD81" t="inlineStr"/>
       <c r="AE81" t="inlineStr"/>
-      <c r="AF81" t="inlineStr"/>
     </row>
     <row r="82" ht="30" customHeight="1" s="17">
       <c r="J82" s="1" t="inlineStr">
@@ -4320,7 +4236,6 @@
       <c r="AC82" t="inlineStr"/>
       <c r="AD82" t="inlineStr"/>
       <c r="AE82" t="inlineStr"/>
-      <c r="AF82" t="inlineStr"/>
     </row>
     <row r="83" ht="30" customHeight="1" s="17">
       <c r="J83" s="1" t="inlineStr">
@@ -4364,7 +4279,6 @@
       <c r="AC83" t="inlineStr"/>
       <c r="AD83" t="inlineStr"/>
       <c r="AE83" t="inlineStr"/>
-      <c r="AF83" t="inlineStr"/>
     </row>
     <row r="84" ht="30" customHeight="1" s="17">
       <c r="J84" s="1" t="inlineStr">
@@ -4412,7 +4326,6 @@
       <c r="AC84" t="inlineStr"/>
       <c r="AD84" t="inlineStr"/>
       <c r="AE84" t="inlineStr"/>
-      <c r="AF84" t="inlineStr"/>
     </row>
     <row r="85" ht="30" customHeight="1" s="17">
       <c r="J85" s="1" t="inlineStr">
@@ -4460,7 +4373,6 @@
       <c r="AC85" t="inlineStr"/>
       <c r="AD85" t="inlineStr"/>
       <c r="AE85" t="inlineStr"/>
-      <c r="AF85" t="inlineStr"/>
     </row>
     <row r="86" ht="30" customHeight="1" s="17">
       <c r="J86" s="1" t="inlineStr">
@@ -4508,7 +4420,6 @@
       <c r="AC86" t="inlineStr"/>
       <c r="AD86" t="inlineStr"/>
       <c r="AE86" t="inlineStr"/>
-      <c r="AF86" t="inlineStr"/>
     </row>
     <row r="87" ht="30" customHeight="1" s="17">
       <c r="J87" s="1" t="inlineStr">
@@ -4552,7 +4463,6 @@
       <c r="AC87" t="inlineStr"/>
       <c r="AD87" t="inlineStr"/>
       <c r="AE87" t="inlineStr"/>
-      <c r="AF87" t="inlineStr"/>
     </row>
     <row r="88" ht="30" customHeight="1" s="17">
       <c r="J88" s="1" t="inlineStr">
@@ -4596,7 +4506,6 @@
       <c r="AC88" t="inlineStr"/>
       <c r="AD88" t="inlineStr"/>
       <c r="AE88" t="inlineStr"/>
-      <c r="AF88" t="inlineStr"/>
     </row>
     <row r="89" ht="30" customHeight="1" s="17">
       <c r="J89" s="1" t="inlineStr">
@@ -4640,7 +4549,6 @@
       <c r="AC89" t="inlineStr"/>
       <c r="AD89" t="inlineStr"/>
       <c r="AE89" t="inlineStr"/>
-      <c r="AF89" t="inlineStr"/>
     </row>
     <row r="90" ht="30" customHeight="1" s="17">
       <c r="J90" s="1" t="inlineStr">
@@ -4684,7 +4592,6 @@
       <c r="AC90" t="inlineStr"/>
       <c r="AD90" t="inlineStr"/>
       <c r="AE90" t="inlineStr"/>
-      <c r="AF90" t="inlineStr"/>
     </row>
     <row r="91" ht="30" customHeight="1" s="17">
       <c r="J91" s="1" t="inlineStr">
@@ -4728,7 +4635,6 @@
       <c r="AC91" t="inlineStr"/>
       <c r="AD91" t="inlineStr"/>
       <c r="AE91" t="inlineStr"/>
-      <c r="AF91" t="inlineStr"/>
     </row>
     <row r="92" ht="30" customHeight="1" s="17">
       <c r="J92" s="1" t="inlineStr">
@@ -4784,7 +4690,6 @@
           <t>枚举值召回无候选枚举代码，判定新增枚举代码并新增标准</t>
         </is>
       </c>
-      <c r="AF92" t="inlineStr"/>
     </row>
     <row r="93" ht="30" customHeight="1" s="17">
       <c r="J93" s="1" t="inlineStr">
@@ -4828,7 +4733,6 @@
       <c r="AC93" t="inlineStr"/>
       <c r="AD93" t="inlineStr"/>
       <c r="AE93" t="inlineStr"/>
-      <c r="AF93" t="inlineStr"/>
     </row>
     <row r="94" ht="30" customHeight="1" s="17">
       <c r="J94" s="1" t="inlineStr">
@@ -4884,7 +4788,6 @@
           <t>枚举值召回无候选枚举代码，判定新增枚举代码并新增标准</t>
         </is>
       </c>
-      <c r="AF94" t="inlineStr"/>
     </row>
     <row r="95" ht="15" customFormat="1" customHeight="1" s="9">
       <c r="J95" s="8" t="inlineStr">
@@ -4925,7 +4828,6 @@
       <c r="AC95" t="inlineStr"/>
       <c r="AD95" t="inlineStr"/>
       <c r="AE95" t="inlineStr"/>
-      <c r="AF95" t="inlineStr"/>
     </row>
     <row r="96" ht="15" customHeight="1" s="17">
       <c r="J96" s="2" t="inlineStr">
@@ -4966,7 +4868,6 @@
       <c r="AC96" t="inlineStr"/>
       <c r="AD96" t="inlineStr"/>
       <c r="AE96" t="inlineStr"/>
-      <c r="AF96" t="inlineStr"/>
     </row>
     <row r="97" ht="30" customHeight="1" s="17">
       <c r="J97" s="2" t="inlineStr">
@@ -5007,7 +4908,6 @@
       <c r="AC97" t="inlineStr"/>
       <c r="AD97" t="inlineStr"/>
       <c r="AE97" t="inlineStr"/>
-      <c r="AF97" t="inlineStr"/>
     </row>
     <row r="98" ht="28.9" customHeight="1" s="17">
       <c r="J98" s="2" t="inlineStr">
@@ -5061,7 +4961,6 @@
           <t>枚举值召回无候选枚举代码，判定新增枚举代码并新增标准</t>
         </is>
       </c>
-      <c r="AF98" t="inlineStr"/>
     </row>
     <row r="99" ht="15" customHeight="1" s="17">
       <c r="J99" s="2" t="inlineStr">
@@ -5102,7 +5001,6 @@
       <c r="AC99" t="inlineStr"/>
       <c r="AD99" t="inlineStr"/>
       <c r="AE99" t="inlineStr"/>
-      <c r="AF99" t="inlineStr"/>
     </row>
     <row r="100" ht="15" customHeight="1" s="17">
       <c r="J100" s="2" t="inlineStr">
@@ -5145,7 +5043,6 @@
       <c r="AC100" t="inlineStr"/>
       <c r="AD100" t="inlineStr"/>
       <c r="AE100" t="inlineStr"/>
-      <c r="AF100" t="inlineStr"/>
     </row>
     <row r="101" ht="30" customHeight="1" s="17">
       <c r="J101" s="2" t="inlineStr">
@@ -5186,7 +5083,6 @@
       <c r="AC101" t="inlineStr"/>
       <c r="AD101" t="inlineStr"/>
       <c r="AE101" t="inlineStr"/>
-      <c r="AF101" t="inlineStr"/>
     </row>
     <row r="102" ht="30" customHeight="1" s="17">
       <c r="J102" s="2" t="inlineStr">
@@ -5227,7 +5123,6 @@
       <c r="AC102" t="inlineStr"/>
       <c r="AD102" t="inlineStr"/>
       <c r="AE102" t="inlineStr"/>
-      <c r="AF102" t="inlineStr"/>
     </row>
     <row r="103" ht="15" customHeight="1" s="17"/>
     <row r="104" ht="30" customHeight="1" s="17"/>
@@ -5499,8 +5394,8 @@
   </sheetData>
   <autoFilter ref="A2:Z378"/>
   <mergeCells count="3">
-    <mergeCell ref="AA1:AF1"/>
     <mergeCell ref="I1:Z1"/>
+    <mergeCell ref="AA1:AE1"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
